--- a/src/Planning_engine/ALICE_BIM_mapper/inputs/ALICE_macro.xlsx
+++ b/src/Planning_engine/ALICE_BIM_mapper/inputs/ALICE_macro.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="370">
   <si>
     <t xml:space="preserve">Alice WBS Id*</t>
   </si>
@@ -236,6 +236,474 @@
     <t xml:space="preserve">Capacity</t>
   </si>
   <si>
+    <t>3837e7c2-0906-4333-ac9b-a2737d9ef3ab</t>
+  </si>
+  <si>
+    <t>Island 2026</t>
+  </si>
+  <si>
+    <t>project</t>
+  </si>
+  <si>
+    <t>cbd410b2-5548-4cd2-8527-f2345a50d57f</t>
+  </si>
+  <si>
+    <t>SITE PREPARATION &amp; DEMOLITION</t>
+  </si>
+  <si>
+    <t>project.SITE PREPARATION &amp; DEMOLITION</t>
+  </si>
+  <si>
+    <t>0d25cbc5-489e-404b-bca9-c37d58b2aab2</t>
+  </si>
+  <si>
+    <t>EARTHWORK &amp; BASEMENT</t>
+  </si>
+  <si>
+    <t>project.EARTHWORK &amp; BASEMENT</t>
+  </si>
+  <si>
+    <t>877325b6-0ec2-4dc8-b9e3-cfa6b8292d16</t>
+  </si>
+  <si>
+    <t>SUPERSTRUCTURE</t>
+  </si>
+  <si>
+    <t>project.SUPERSTRUCTURE – ZONE A</t>
+  </si>
+  <si>
+    <t>63195f08-e779-4f3a-ae3a-306d40e10c1c</t>
+  </si>
+  <si>
+    <t>ENVELOPE</t>
+  </si>
+  <si>
+    <t>project.ENVELOPE</t>
+  </si>
+  <si>
+    <t>c3929e98-3e87-4181-a90c-ec2646e7d440</t>
+  </si>
+  <si>
+    <t>MEP INSTALLATION</t>
+  </si>
+  <si>
+    <t>project.MEP INSTALLATION</t>
+  </si>
+  <si>
+    <t>da7c403f-4319-48fd-8009-37270386cab6</t>
+  </si>
+  <si>
+    <t>INTERIOR</t>
+  </si>
+  <si>
+    <t>project.INTERIOR FINISHES</t>
+  </si>
+  <si>
+    <t>383f728a-1104-4558-be7b-db47650d4deb</t>
+  </si>
+  <si>
+    <t>COMMISSIONING &amp; CLOSEOUT</t>
+  </si>
+  <si>
+    <t>project.COMMISSIONING &amp; CLOSEOUT</t>
+  </si>
+  <si>
+    <t>A1070</t>
+  </si>
+  <si>
+    <t>Site Setup Crew</t>
+  </si>
+  <si>
+    <t>A1080</t>
+  </si>
+  <si>
+    <t>A1090</t>
+  </si>
+  <si>
+    <t>A1100</t>
+  </si>
+  <si>
+    <t>A1110</t>
+  </si>
+  <si>
+    <t>Tree Removal / Clearing Crew</t>
+  </si>
+  <si>
+    <t>A1120</t>
+  </si>
+  <si>
+    <t>Demolition Crew (bleachers)</t>
+  </si>
+  <si>
+    <t>A1140</t>
+  </si>
+  <si>
+    <t>A1150</t>
+  </si>
+  <si>
+    <t>A1170</t>
+  </si>
+  <si>
+    <t>Earthwork Crew (excavation)</t>
+  </si>
+  <si>
+    <t>A1180</t>
+  </si>
+  <si>
+    <t>Shoring / Stabilization Crew</t>
+  </si>
+  <si>
+    <t>A1190</t>
+  </si>
+  <si>
+    <t>A1200</t>
+  </si>
+  <si>
+    <t>Concrete Crew</t>
+  </si>
+  <si>
+    <t>A1210</t>
+  </si>
+  <si>
+    <t>A1220</t>
+  </si>
+  <si>
+    <t>A1230</t>
+  </si>
+  <si>
+    <t>A1240</t>
+  </si>
+  <si>
+    <t>A1250</t>
+  </si>
+  <si>
+    <t>Underground Utilities Crew</t>
+  </si>
+  <si>
+    <t>A1260</t>
+  </si>
+  <si>
+    <t>Exc</t>
+  </si>
+  <si>
+    <t>A1270</t>
+  </si>
+  <si>
+    <t>A1280</t>
+  </si>
+  <si>
+    <t>Structural Crew</t>
+  </si>
+  <si>
+    <t>A1330</t>
+  </si>
+  <si>
+    <t>A1340</t>
+  </si>
+  <si>
+    <t>A1420</t>
+  </si>
+  <si>
+    <t>A1590</t>
+  </si>
+  <si>
+    <t>Facade Install Crew</t>
+  </si>
+  <si>
+    <t>A1610</t>
+  </si>
+  <si>
+    <t>A1670</t>
+  </si>
+  <si>
+    <t>HVAC Rough-In Crew</t>
+  </si>
+  <si>
+    <t>A1680</t>
+  </si>
+  <si>
+    <t>Electrical Rough-In Crew</t>
+  </si>
+  <si>
+    <t>A1690</t>
+  </si>
+  <si>
+    <t>Plumbing + Fire Protection Rough-In Crew</t>
+  </si>
+  <si>
+    <t>A1740</t>
+  </si>
+  <si>
+    <t>Interiors Crew</t>
+  </si>
+  <si>
+    <t>A1760</t>
+  </si>
+  <si>
+    <t>A1820</t>
+  </si>
+  <si>
+    <t>Commissioning / Controls Support</t>
+  </si>
+  <si>
+    <t>A1830</t>
+  </si>
+  <si>
+    <t>TAB Team</t>
+  </si>
+  <si>
+    <t>A1840</t>
+  </si>
+  <si>
+    <t>A1860</t>
+  </si>
+  <si>
+    <t>commissioning_controls_support</t>
+  </si>
+  <si>
+    <t>Default calendar</t>
+  </si>
+  <si>
+    <t>#fc5555</t>
+  </si>
+  <si>
+    <t>Commissioning Crew</t>
+  </si>
+  <si>
+    <t>commissioning_crew</t>
+  </si>
+  <si>
+    <t>concrete_crew</t>
+  </si>
+  <si>
+    <t>#fea4a4</t>
+  </si>
+  <si>
+    <t>Concrete Topping Crew</t>
+  </si>
+  <si>
+    <t>concrete_topping_crew</t>
+  </si>
+  <si>
+    <t>#f4c2fe</t>
+  </si>
+  <si>
+    <t>Core Crew</t>
+  </si>
+  <si>
+    <t>core_crew</t>
+  </si>
+  <si>
+    <t>#79f6f6</t>
+  </si>
+  <si>
+    <t>Deck Install Crew</t>
+  </si>
+  <si>
+    <t>deck_install_crew</t>
+  </si>
+  <si>
+    <t>#cdc3fe</t>
+  </si>
+  <si>
+    <t>demolition_crew_bleachers_</t>
+  </si>
+  <si>
+    <t>#6549f3</t>
+  </si>
+  <si>
+    <t>Drywall Robot Crew</t>
+  </si>
+  <si>
+    <t>drywall_robot_crew</t>
+  </si>
+  <si>
+    <t>Earthwork Crew</t>
+  </si>
+  <si>
+    <t>earthwork_crew</t>
+  </si>
+  <si>
+    <t>5dx10hr</t>
+  </si>
+  <si>
+    <t>#67cc5c</t>
+  </si>
+  <si>
+    <t>earthwork_crew_excavation_</t>
+  </si>
+  <si>
+    <t>#ce6fe2</t>
+  </si>
+  <si>
+    <t>electrical_rough_in_crew</t>
+  </si>
+  <si>
+    <t>exc</t>
+  </si>
+  <si>
+    <t>#a5fd9b</t>
+  </si>
+  <si>
+    <t>facade_install_crew</t>
+  </si>
+  <si>
+    <t>Facade Install Crew 1</t>
+  </si>
+  <si>
+    <t>facade_install_crew_1</t>
+  </si>
+  <si>
+    <t>Facade Install Crew 2</t>
+  </si>
+  <si>
+    <t>facade_install_crew_2</t>
+  </si>
+  <si>
+    <t>Facade Robot Crew</t>
+  </si>
+  <si>
+    <t>facade_robot_crew</t>
+  </si>
+  <si>
+    <t>Finishes Crew</t>
+  </si>
+  <si>
+    <t>finishes_crew</t>
+  </si>
+  <si>
+    <t>Flooring Crew</t>
+  </si>
+  <si>
+    <t>flooring_crew</t>
+  </si>
+  <si>
+    <t>hvac_rough_in_crew</t>
+  </si>
+  <si>
+    <t>Interior Framing Crew</t>
+  </si>
+  <si>
+    <t>interior_framing_crew</t>
+  </si>
+  <si>
+    <t>Interior Framing/Drywall Crew</t>
+  </si>
+  <si>
+    <t>interior_framing_drywall_crew</t>
+  </si>
+  <si>
+    <t>interiors_crew</t>
+  </si>
+  <si>
+    <t>MEP Rough-In Crew</t>
+  </si>
+  <si>
+    <t>mep_rough_in_crew</t>
+  </si>
+  <si>
+    <t>Mobile Crane</t>
+  </si>
+  <si>
+    <t>mobile_crane</t>
+  </si>
+  <si>
+    <t>plumbing_fire_protection_rough_in_crew</t>
+  </si>
+  <si>
+    <t>Pour Strip Closure Crew</t>
+  </si>
+  <si>
+    <t>pour_strip_closure_crew</t>
+  </si>
+  <si>
+    <t>#f679af</t>
+  </si>
+  <si>
+    <t>Rebar Crew</t>
+  </si>
+  <si>
+    <t>rebar_crew</t>
+  </si>
+  <si>
+    <t>Roofing Crew</t>
+  </si>
+  <si>
+    <t>roofing_crew</t>
+  </si>
+  <si>
+    <t>shoring_stabilization_crew</t>
+  </si>
+  <si>
+    <t>#d8317a</t>
+  </si>
+  <si>
+    <t>site_setup_crew</t>
+  </si>
+  <si>
+    <t>#fc8c55</t>
+  </si>
+  <si>
+    <t>Steel Erection Crew</t>
+  </si>
+  <si>
+    <t>steel_erection_crew</t>
+  </si>
+  <si>
+    <t>Steel Fabrication Crew</t>
+  </si>
+  <si>
+    <t>steel_fabrication_crew</t>
+  </si>
+  <si>
+    <t>structural_crew</t>
+  </si>
+  <si>
+    <t>#a5d1fd</t>
+  </si>
+  <si>
+    <t>tab_team</t>
+  </si>
+  <si>
+    <t>Temp Power/Electrical</t>
+  </si>
+  <si>
+    <t>temp_power_electrical</t>
+  </si>
+  <si>
+    <t>#fdd50d</t>
+  </si>
+  <si>
+    <t>Temp Water/Plumbing</t>
+  </si>
+  <si>
+    <t>temp_water_plumbing</t>
+  </si>
+  <si>
+    <t>#45c4c4</t>
+  </si>
+  <si>
+    <t>tree_removal_clearing_crew</t>
+  </si>
+  <si>
+    <t>#4ba3fc</t>
+  </si>
+  <si>
+    <t>underground_utilities_crew</t>
+  </si>
+  <si>
+    <t>#feea86</t>
+  </si>
+  <si>
+    <t>Waterproofing &amp; Drainage Crew</t>
+  </si>
+  <si>
+    <t>waterproofing_drainage_crew</t>
+  </si>
+  <si>
+    <t>#e4cbbe</t>
+  </si>
+  <si>
     <t>Backfill/Compaction (cy/hr)</t>
   </si>
   <si>
@@ -278,151 +746,358 @@
     <t>slab_on_grade_sf_hr_</t>
   </si>
   <si>
-    <t>A1070</t>
-  </si>
-  <si>
-    <t>Site Setup Crew</t>
-  </si>
-  <si>
-    <t>A1080</t>
-  </si>
-  <si>
-    <t>A1090</t>
-  </si>
-  <si>
-    <t>A1100</t>
-  </si>
-  <si>
-    <t>A1110</t>
-  </si>
-  <si>
-    <t>Tree Removal / Clearing Crew</t>
-  </si>
-  <si>
-    <t>A1120</t>
-  </si>
-  <si>
-    <t>Demolition Crew (bleachers)</t>
-  </si>
-  <si>
-    <t>A1140</t>
-  </si>
-  <si>
-    <t>A1150</t>
-  </si>
-  <si>
-    <t>A1170</t>
-  </si>
-  <si>
-    <t>Earthwork Crew (excavation)</t>
-  </si>
-  <si>
-    <t>A1180</t>
-  </si>
-  <si>
-    <t>Shoring / Stabilization Crew</t>
-  </si>
-  <si>
-    <t>A1190</t>
-  </si>
-  <si>
-    <t>A1200</t>
-  </si>
-  <si>
-    <t>Concrete Crew</t>
-  </si>
-  <si>
-    <t>A1210</t>
-  </si>
-  <si>
-    <t>A1220</t>
-  </si>
-  <si>
-    <t>A1230</t>
-  </si>
-  <si>
-    <t>A1240</t>
-  </si>
-  <si>
-    <t>A1250</t>
-  </si>
-  <si>
-    <t>Underground Utilities Crew</t>
-  </si>
-  <si>
-    <t>A1260</t>
-  </si>
-  <si>
-    <t>Exc</t>
-  </si>
-  <si>
-    <t>A1270</t>
-  </si>
-  <si>
-    <t>A1330</t>
-  </si>
-  <si>
-    <t>Structural Crew</t>
-  </si>
-  <si>
-    <t>A1340</t>
-  </si>
-  <si>
-    <t>A1420</t>
-  </si>
-  <si>
-    <t>A1590</t>
-  </si>
-  <si>
-    <t>Facade Install Crew</t>
-  </si>
-  <si>
-    <t>A1610</t>
-  </si>
-  <si>
-    <t>A1670</t>
-  </si>
-  <si>
-    <t>HVAC Rough-In Crew</t>
-  </si>
-  <si>
-    <t>A1680</t>
-  </si>
-  <si>
-    <t>Electrical Rough-In Crew</t>
-  </si>
-  <si>
-    <t>A1690</t>
-  </si>
-  <si>
-    <t>Plumbing + Fire Protection Rough-In Crew</t>
-  </si>
-  <si>
-    <t>A1740</t>
-  </si>
-  <si>
-    <t>Interiors Crew</t>
-  </si>
-  <si>
-    <t>A1760</t>
-  </si>
-  <si>
-    <t>A1820</t>
-  </si>
-  <si>
-    <t>Commissioning / Controls Support</t>
-  </si>
-  <si>
-    <t>A1830</t>
-  </si>
-  <si>
-    <t>TAB Team</t>
-  </si>
-  <si>
-    <t>A1840</t>
-  </si>
-  <si>
-    <t>A1860</t>
+    <t>Excavator</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Compactor/Roller</t>
+  </si>
+  <si>
+    <t>Concrete Pump</t>
+  </si>
+  <si>
+    <t>FS</t>
+  </si>
+  <si>
+    <t>A1350</t>
+  </si>
+  <si>
+    <t>A1600</t>
+  </si>
+  <si>
+    <t>A1880</t>
+  </si>
+  <si>
+    <t>Install Construction Fencing</t>
+  </si>
+  <si>
+    <t>REGULAR</t>
+  </si>
+  <si>
+    <t>MANUAL</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>NOT_STARTED</t>
+  </si>
+  <si>
+    <t>2029-10-01T09:00</t>
+  </si>
+  <si>
+    <t>2029-10-03T17:00</t>
+  </si>
+  <si>
+    <t>Install Site Office &amp; Welfare Units</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>2029-10-04T09:00</t>
+  </si>
+  <si>
+    <t>2029-10-09T17:00</t>
+  </si>
+  <si>
+    <t>Temporary Water Installation</t>
+  </si>
+  <si>
+    <t>2029-10-08T17:00</t>
+  </si>
+  <si>
+    <t>Temporary Power Installation</t>
+  </si>
+  <si>
+    <t>Tree Removal &amp; Clearing</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>2029-10-10T17:00</t>
+  </si>
+  <si>
+    <t>Bleacher Demolition</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>2029-10-12T17:00</t>
+  </si>
+  <si>
+    <t>Crane Pad Construction</t>
+  </si>
+  <si>
+    <t>2029-10-11T09:00</t>
+  </si>
+  <si>
+    <t>2029-10-17T17:00</t>
+  </si>
+  <si>
+    <t>Laydown Area Preparation</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>2029-10-11T17:00</t>
+  </si>
+  <si>
+    <t>Full Basement Excavation</t>
+  </si>
+  <si>
+    <t>Shoring / Stabilization</t>
+  </si>
+  <si>
+    <t>2029-10-10T09:00</t>
+  </si>
+  <si>
+    <t>2029-10-16T17:00</t>
+  </si>
+  <si>
+    <t>Subgrade Preparation</t>
+  </si>
+  <si>
+    <t>2029-10-15T17:00</t>
+  </si>
+  <si>
+    <t>Footings – Form/Rebar/Pour</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>2029-11-08T09:00</t>
+  </si>
+  <si>
+    <t>2029-11-21T17:00</t>
+  </si>
+  <si>
+    <t>Grade Beams</t>
+  </si>
+  <si>
+    <t>2029-12-03T09:00</t>
+  </si>
+  <si>
+    <t>2029-12-11T17:00</t>
+  </si>
+  <si>
+    <t>Basement Retaining Walls</t>
+  </si>
+  <si>
+    <t>2029-11-05T09:00</t>
+  </si>
+  <si>
+    <t>2029-11-07T17:00</t>
+  </si>
+  <si>
+    <t>Waterproofing &amp; Drainage</t>
+  </si>
+  <si>
+    <t>2029-10-18T09:00</t>
+  </si>
+  <si>
+    <t>2029-10-24T17:00</t>
+  </si>
+  <si>
+    <t>Basement Slab on Grade</t>
+  </si>
+  <si>
+    <t>2029-12-12T09:00</t>
+  </si>
+  <si>
+    <t>2029-12-20T17:00</t>
+  </si>
+  <si>
+    <t>Underground Utilities</t>
+  </si>
+  <si>
+    <t>2029-10-25T09:00</t>
+  </si>
+  <si>
+    <t>2029-11-02T17:00</t>
+  </si>
+  <si>
+    <t>Backfill &amp; Compaction</t>
+  </si>
+  <si>
+    <t>2029-11-14T17:00</t>
+  </si>
+  <si>
+    <t>Foundational Columns</t>
+  </si>
+  <si>
+    <t>2029-11-22T09:00</t>
+  </si>
+  <si>
+    <t>2029-11-30T17:00</t>
+  </si>
+  <si>
+    <t>Rocking Walls</t>
+  </si>
+  <si>
+    <t>2029-12-21T09:00</t>
+  </si>
+  <si>
+    <t>2029-12-27T17:00</t>
+  </si>
+  <si>
+    <t>Frame: Columns</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>2029-12-28T09:00</t>
+  </si>
+  <si>
+    <t>2030-01-04T17:00</t>
+  </si>
+  <si>
+    <t>Floor</t>
+  </si>
+  <si>
+    <t>2030-01-15T09:00</t>
+  </si>
+  <si>
+    <t>2030-01-17T17:00</t>
+  </si>
+  <si>
+    <t>Frame: Beams</t>
+  </si>
+  <si>
+    <t>2030-01-07T09:00</t>
+  </si>
+  <si>
+    <t>2030-01-14T17:00</t>
+  </si>
+  <si>
+    <t>Roof</t>
+  </si>
+  <si>
+    <t>2030-01-18T09:00</t>
+  </si>
+  <si>
+    <t>2030-01-23T17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glass Install + Glazing </t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>2030-02-15T09:00</t>
+  </si>
+  <si>
+    <t>2030-03-08T17:00</t>
+  </si>
+  <si>
+    <t>Exterior Wall Install</t>
+  </si>
+  <si>
+    <t>2030-01-24T09:00</t>
+  </si>
+  <si>
+    <t>2030-02-14T17:00</t>
+  </si>
+  <si>
+    <t>Mesh Install</t>
+  </si>
+  <si>
+    <t>2030-03-11T09:00</t>
+  </si>
+  <si>
+    <t>2030-04-01T17:00</t>
+  </si>
+  <si>
+    <t>Mechanical Room Buildout</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>2030-03-28T17:00</t>
+  </si>
+  <si>
+    <t>Main Electrical &amp; Riser Install</t>
+  </si>
+  <si>
+    <t>MEP Rough-In</t>
+  </si>
+  <si>
+    <t>384</t>
+  </si>
+  <si>
+    <t>2030-03-29T09:00</t>
+  </si>
+  <si>
+    <t>2030-06-04T17:00</t>
+  </si>
+  <si>
+    <t>Interior Walls</t>
+  </si>
+  <si>
+    <t>288</t>
+  </si>
+  <si>
+    <t>2030-04-29T17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceiling Installation </t>
+  </si>
+  <si>
+    <t>2030-04-30T09:00</t>
+  </si>
+  <si>
+    <t>2030-05-21T17:00</t>
+  </si>
+  <si>
+    <t>MEP Start-Up</t>
+  </si>
+  <si>
+    <t>2030-05-22T09:00</t>
+  </si>
+  <si>
+    <t>2030-05-30T17:00</t>
+  </si>
+  <si>
+    <t>TAB</t>
+  </si>
+  <si>
+    <t>2030-05-31T09:00</t>
+  </si>
+  <si>
+    <t>2030-06-10T17:00</t>
+  </si>
+  <si>
+    <t>Integrated Systems Testing</t>
+  </si>
+  <si>
+    <t>2030-06-11T09:00</t>
+  </si>
+  <si>
+    <t>2030-06-17T17:00</t>
+  </si>
+  <si>
+    <t>Final Inspections</t>
+  </si>
+  <si>
+    <t>2030-05-28T17:00</t>
+  </si>
+  <si>
+    <t>Hurricane Contingency Buffer</t>
+  </si>
+  <si>
+    <t>2030-06-18T09:00</t>
+  </si>
+  <si>
+    <t>2030-07-05T17:00</t>
   </si>
   <si>
     <t>Total Cost</t>
@@ -434,435 +1109,9 @@
     <t>CONSUMABLE</t>
   </si>
   <si>
-    <t>3837e7c2-0906-4333-ac9b-a2737d9ef3ab</t>
-  </si>
-  <si>
-    <t>Island 2026</t>
-  </si>
-  <si>
-    <t>project</t>
-  </si>
-  <si>
-    <t>cbd410b2-5548-4cd2-8527-f2345a50d57f</t>
-  </si>
-  <si>
-    <t>SITE PREPARATION &amp; DEMOLITION</t>
-  </si>
-  <si>
-    <t>project.SITE PREPARATION &amp; DEMOLITION</t>
-  </si>
-  <si>
-    <t>0d25cbc5-489e-404b-bca9-c37d58b2aab2</t>
-  </si>
-  <si>
-    <t>EARTHWORK &amp; BASEMENT</t>
-  </si>
-  <si>
-    <t>project.EARTHWORK &amp; BASEMENT</t>
-  </si>
-  <si>
-    <t>877325b6-0ec2-4dc8-b9e3-cfa6b8292d16</t>
-  </si>
-  <si>
-    <t>SUPERSTRUCTURE</t>
-  </si>
-  <si>
-    <t>project.SUPERSTRUCTURE – ZONE A</t>
-  </si>
-  <si>
-    <t>63195f08-e779-4f3a-ae3a-306d40e10c1c</t>
-  </si>
-  <si>
-    <t>ENVELOPE</t>
-  </si>
-  <si>
-    <t>project.ENVELOPE</t>
-  </si>
-  <si>
-    <t>c3929e98-3e87-4181-a90c-ec2646e7d440</t>
-  </si>
-  <si>
-    <t>MEP INSTALLATION</t>
-  </si>
-  <si>
-    <t>project.MEP INSTALLATION</t>
-  </si>
-  <si>
-    <t>da7c403f-4319-48fd-8009-37270386cab6</t>
-  </si>
-  <si>
-    <t>INTERIOR</t>
-  </si>
-  <si>
-    <t>project.INTERIOR FINISHES</t>
-  </si>
-  <si>
-    <t>383f728a-1104-4558-be7b-db47650d4deb</t>
-  </si>
-  <si>
-    <t>COMMISSIONING &amp; CLOSEOUT</t>
-  </si>
-  <si>
-    <t>project.COMMISSIONING &amp; CLOSEOUT</t>
-  </si>
-  <si>
-    <t>Install Construction Fencing</t>
-  </si>
-  <si>
-    <t>REGULAR</t>
-  </si>
-  <si>
-    <t>MANUAL</t>
-  </si>
-  <si>
-    <t>Default calendar</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>NOT_STARTED</t>
-  </si>
-  <si>
-    <t>2029-10-01T09:00</t>
-  </si>
-  <si>
-    <t>2029-10-03T17:00</t>
-  </si>
-  <si>
-    <t>Install Site Office &amp; Welfare Units</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>2029-10-04T09:00</t>
-  </si>
-  <si>
-    <t>2029-10-09T17:00</t>
-  </si>
-  <si>
-    <t>Temporary Water Installation</t>
-  </si>
-  <si>
-    <t>2029-10-08T17:00</t>
-  </si>
-  <si>
-    <t>Temporary Power Installation</t>
-  </si>
-  <si>
-    <t>Tree Removal &amp; Clearing</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>2029-10-10T17:00</t>
-  </si>
-  <si>
-    <t>Bleacher Demolition</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>2029-10-12T17:00</t>
-  </si>
-  <si>
-    <t>Crane Pad Construction</t>
-  </si>
-  <si>
-    <t>2029-10-11T09:00</t>
-  </si>
-  <si>
-    <t>2029-10-17T17:00</t>
-  </si>
-  <si>
-    <t>Laydown Area Preparation</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Full Basement Excavation</t>
-  </si>
-  <si>
-    <t>Shoring / Stabilization</t>
-  </si>
-  <si>
-    <t>2029-10-10T09:00</t>
-  </si>
-  <si>
-    <t>2029-10-16T17:00</t>
-  </si>
-  <si>
-    <t>Subgrade Preparation</t>
-  </si>
-  <si>
-    <t>2029-10-15T17:00</t>
-  </si>
-  <si>
-    <t>Footings – Form/Rebar/Pour</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>2029-10-16T09:00</t>
-  </si>
-  <si>
-    <t>2029-10-29T17:00</t>
-  </si>
-  <si>
-    <t>Grade Beams</t>
-  </si>
-  <si>
-    <t>2029-11-08T09:00</t>
-  </si>
-  <si>
-    <t>2029-11-16T17:00</t>
-  </si>
-  <si>
-    <t>Basement Retaining Walls</t>
-  </si>
-  <si>
-    <t>2029-11-19T09:00</t>
-  </si>
-  <si>
-    <t>2029-11-21T17:00</t>
-  </si>
-  <si>
-    <t>Waterproofing &amp; Drainage</t>
-  </si>
-  <si>
-    <t>2029-11-22T09:00</t>
-  </si>
-  <si>
-    <t>2029-11-28T17:00</t>
-  </si>
-  <si>
-    <t>Basement Slab on Grade</t>
-  </si>
-  <si>
-    <t>2029-12-17T09:00</t>
-  </si>
-  <si>
-    <t>2029-12-25T17:00</t>
-  </si>
-  <si>
-    <t>Underground Utilities</t>
-  </si>
-  <si>
-    <t>2029-11-29T09:00</t>
-  </si>
-  <si>
-    <t>2029-12-07T17:00</t>
-  </si>
-  <si>
-    <t>Backfill &amp; Compaction</t>
-  </si>
-  <si>
-    <t>2029-12-10T09:00</t>
-  </si>
-  <si>
-    <t>2029-12-14T17:00</t>
-  </si>
-  <si>
-    <t>Foundational Columns</t>
-  </si>
-  <si>
-    <t>2029-10-30T09:00</t>
-  </si>
-  <si>
-    <t>2029-11-07T17:00</t>
-  </si>
-  <si>
-    <t>Frame: Columns</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>2030-01-08T09:00</t>
-  </si>
-  <si>
-    <t>2030-01-15T17:00</t>
-  </si>
-  <si>
-    <t>Floor</t>
-  </si>
-  <si>
-    <t>2030-01-03T09:00</t>
-  </si>
-  <si>
-    <t>2030-01-07T17:00</t>
-  </si>
-  <si>
-    <t>A1350</t>
-  </si>
-  <si>
-    <t>Frame: Beams</t>
-  </si>
-  <si>
-    <t>2029-12-26T09:00</t>
-  </si>
-  <si>
-    <t>2030-01-02T17:00</t>
-  </si>
-  <si>
-    <t>Roof</t>
-  </si>
-  <si>
-    <t>2030-01-16T09:00</t>
-  </si>
-  <si>
-    <t>2030-01-21T17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glass Install + Glazing </t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>2030-02-13T09:00</t>
-  </si>
-  <si>
-    <t>2030-03-06T17:00</t>
-  </si>
-  <si>
-    <t>A1600</t>
-  </si>
-  <si>
-    <t>Exterior Wall Install</t>
-  </si>
-  <si>
-    <t>2030-01-22T09:00</t>
-  </si>
-  <si>
-    <t>2030-02-12T17:00</t>
-  </si>
-  <si>
-    <t>Mesh Install</t>
-  </si>
-  <si>
-    <t>2030-03-07T09:00</t>
-  </si>
-  <si>
-    <t>2030-03-28T17:00</t>
-  </si>
-  <si>
-    <t>Mechanical Room Buildout</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>2030-03-26T17:00</t>
-  </si>
-  <si>
-    <t>Main Electrical &amp; Riser Install</t>
-  </si>
-  <si>
-    <t>MEP Rough-In</t>
-  </si>
-  <si>
-    <t>384</t>
-  </si>
-  <si>
-    <t>2030-03-27T09:00</t>
-  </si>
-  <si>
-    <t>2030-05-31T17:00</t>
-  </si>
-  <si>
-    <t>Interior Walls</t>
-  </si>
-  <si>
-    <t>288</t>
-  </si>
-  <si>
-    <t>2030-04-25T17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceiling Installation </t>
-  </si>
-  <si>
-    <t>2030-04-26T09:00</t>
-  </si>
-  <si>
-    <t>2030-05-17T17:00</t>
-  </si>
-  <si>
-    <t>MEP Start-Up</t>
-  </si>
-  <si>
-    <t>2030-05-20T09:00</t>
-  </si>
-  <si>
-    <t>2030-05-28T17:00</t>
-  </si>
-  <si>
-    <t>TAB</t>
-  </si>
-  <si>
-    <t>2030-05-29T09:00</t>
-  </si>
-  <si>
-    <t>2030-06-06T17:00</t>
-  </si>
-  <si>
-    <t>Integrated Systems Testing</t>
-  </si>
-  <si>
-    <t>2030-06-07T09:00</t>
-  </si>
-  <si>
-    <t>2030-06-13T17:00</t>
-  </si>
-  <si>
-    <t>Final Inspections</t>
-  </si>
-  <si>
-    <t>2030-05-24T17:00</t>
-  </si>
-  <si>
-    <t>A1880</t>
-  </si>
-  <si>
-    <t>Hurricane Contingency Buffer</t>
-  </si>
-  <si>
-    <t>2030-06-14T09:00</t>
-  </si>
-  <si>
-    <t>2030-07-03T17:00</t>
-  </si>
-  <si>
-    <t>Excavator</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Compactor/Roller</t>
-  </si>
-  <si>
-    <t>Concrete Pump</t>
-  </si>
-  <si>
-    <t>Mobile Crane</t>
-  </si>
-  <si>
-    <t>FS</t>
-  </si>
-  <si>
     <t>compactor_roller</t>
   </si>
   <si>
-    <t>5dx10hr</t>
-  </si>
-  <si>
     <t>concrete_pump</t>
   </si>
   <si>
@@ -887,247 +1136,10 @@
     <t>forklift_telehandler</t>
   </si>
   <si>
-    <t>mobile_crane</t>
-  </si>
-  <si>
-    <t>#a5fd9b</t>
-  </si>
-  <si>
     <t>Scissor Lift</t>
   </si>
   <si>
     <t>scissor_lift</t>
-  </si>
-  <si>
-    <t>commissioning_controls_support</t>
-  </si>
-  <si>
-    <t>#fc5555</t>
-  </si>
-  <si>
-    <t>Commissioning Crew</t>
-  </si>
-  <si>
-    <t>commissioning_crew</t>
-  </si>
-  <si>
-    <t>concrete_crew</t>
-  </si>
-  <si>
-    <t>#fea4a4</t>
-  </si>
-  <si>
-    <t>Concrete Topping Crew</t>
-  </si>
-  <si>
-    <t>concrete_topping_crew</t>
-  </si>
-  <si>
-    <t>#f4c2fe</t>
-  </si>
-  <si>
-    <t>Core Crew</t>
-  </si>
-  <si>
-    <t>core_crew</t>
-  </si>
-  <si>
-    <t>#79f6f6</t>
-  </si>
-  <si>
-    <t>Deck Install Crew</t>
-  </si>
-  <si>
-    <t>deck_install_crew</t>
-  </si>
-  <si>
-    <t>#cdc3fe</t>
-  </si>
-  <si>
-    <t>demolition_crew_bleachers_</t>
-  </si>
-  <si>
-    <t>#6549f3</t>
-  </si>
-  <si>
-    <t>Drywall Robot Crew</t>
-  </si>
-  <si>
-    <t>drywall_robot_crew</t>
-  </si>
-  <si>
-    <t>Earthwork Crew</t>
-  </si>
-  <si>
-    <t>earthwork_crew</t>
-  </si>
-  <si>
-    <t>#67cc5c</t>
-  </si>
-  <si>
-    <t>earthwork_crew_excavation_</t>
-  </si>
-  <si>
-    <t>#ce6fe2</t>
-  </si>
-  <si>
-    <t>electrical_rough_in_crew</t>
-  </si>
-  <si>
-    <t>exc</t>
-  </si>
-  <si>
-    <t>facade_install_crew</t>
-  </si>
-  <si>
-    <t>Facade Install Crew 1</t>
-  </si>
-  <si>
-    <t>facade_install_crew_1</t>
-  </si>
-  <si>
-    <t>Facade Install Crew 2</t>
-  </si>
-  <si>
-    <t>facade_install_crew_2</t>
-  </si>
-  <si>
-    <t>Facade Robot Crew</t>
-  </si>
-  <si>
-    <t>facade_robot_crew</t>
-  </si>
-  <si>
-    <t>Finishes Crew</t>
-  </si>
-  <si>
-    <t>finishes_crew</t>
-  </si>
-  <si>
-    <t>Flooring Crew</t>
-  </si>
-  <si>
-    <t>flooring_crew</t>
-  </si>
-  <si>
-    <t>hvac_rough_in_crew</t>
-  </si>
-  <si>
-    <t>Interior Framing Crew</t>
-  </si>
-  <si>
-    <t>interior_framing_crew</t>
-  </si>
-  <si>
-    <t>Interior Framing/Drywall Crew</t>
-  </si>
-  <si>
-    <t>interior_framing_drywall_crew</t>
-  </si>
-  <si>
-    <t>interiors_crew</t>
-  </si>
-  <si>
-    <t>MEP Rough-In Crew</t>
-  </si>
-  <si>
-    <t>mep_rough_in_crew</t>
-  </si>
-  <si>
-    <t>plumbing_fire_protection_rough_in_crew</t>
-  </si>
-  <si>
-    <t>Pour Strip Closure Crew</t>
-  </si>
-  <si>
-    <t>pour_strip_closure_crew</t>
-  </si>
-  <si>
-    <t>#f679af</t>
-  </si>
-  <si>
-    <t>Rebar Crew</t>
-  </si>
-  <si>
-    <t>rebar_crew</t>
-  </si>
-  <si>
-    <t>Roofing Crew</t>
-  </si>
-  <si>
-    <t>roofing_crew</t>
-  </si>
-  <si>
-    <t>shoring_stabilization_crew</t>
-  </si>
-  <si>
-    <t>#d8317a</t>
-  </si>
-  <si>
-    <t>site_setup_crew</t>
-  </si>
-  <si>
-    <t>#fc8c55</t>
-  </si>
-  <si>
-    <t>Steel Erection Crew</t>
-  </si>
-  <si>
-    <t>steel_erection_crew</t>
-  </si>
-  <si>
-    <t>Steel Fabrication Crew</t>
-  </si>
-  <si>
-    <t>steel_fabrication_crew</t>
-  </si>
-  <si>
-    <t>structural_crew</t>
-  </si>
-  <si>
-    <t>#a5d1fd</t>
-  </si>
-  <si>
-    <t>tab_team</t>
-  </si>
-  <si>
-    <t>Temp Power/Electrical</t>
-  </si>
-  <si>
-    <t>temp_power_electrical</t>
-  </si>
-  <si>
-    <t>#fdd50d</t>
-  </si>
-  <si>
-    <t>Temp Water/Plumbing</t>
-  </si>
-  <si>
-    <t>temp_water_plumbing</t>
-  </si>
-  <si>
-    <t>#45c4c4</t>
-  </si>
-  <si>
-    <t>tree_removal_clearing_crew</t>
-  </si>
-  <si>
-    <t>#4ba3fc</t>
-  </si>
-  <si>
-    <t>underground_utilities_crew</t>
-  </si>
-  <si>
-    <t>#feea86</t>
-  </si>
-  <si>
-    <t>Waterproofing &amp; Drainage Crew</t>
-  </si>
-  <si>
-    <t>waterproofing_drainage_crew</t>
-  </si>
-  <si>
-    <t>#e4cbbe</t>
   </si>
 </sst>
 </file>
@@ -1463,114 +1475,114 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="C2" t="n">
         <v>1.0</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
         <v>2.0</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="C4" t="n">
         <v>2.0</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="C5" t="n">
         <v>2.0</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C6" t="n">
         <v>2.0</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
         <v>2.0</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
         <v>2.0</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
-        <v>156</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>2.0</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1610,10 +1622,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>224</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>225</v>
       </c>
       <c r="C2" t="n">
         <v>35.0</v>
@@ -1621,10 +1633,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>226</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="C3" t="n">
         <v>200.0</v>
@@ -1632,10 +1644,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>228</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>229</v>
       </c>
       <c r="C4" t="n">
         <v>30.0</v>
@@ -1643,10 +1655,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>230</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>231</v>
       </c>
       <c r="C5" t="n">
         <v>250.0</v>
@@ -1654,10 +1666,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>232</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="C6" t="n">
         <v>40.0</v>
@@ -1665,10 +1677,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="C7" t="n">
         <v>2000.0</v>
@@ -1676,10 +1688,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>236</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>237</v>
       </c>
       <c r="C8" t="n">
         <v>300.0</v>
@@ -1740,7 +1752,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:AB37"/>
+  <dimension ref="A2:AB38"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="24" max="24" customWidth="true" hidden="false" style="0" width="20.0" collapsed="false" outlineLevel="0"/>
@@ -1862,35 +1874,35 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>246</v>
       </c>
       <c r="C2" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D2" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G2" t="s">
-        <v>162</v>
+        <v>249</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="K2" t="s">
-        <v>165</v>
+        <v>252</v>
       </c>
       <c r="L2" t="n">
         <v>0.0</v>
@@ -1902,10 +1914,10 @@
       <c r="Q2"/>
       <c r="R2"/>
       <c r="S2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="T2" t="s">
-        <v>165</v>
+        <v>252</v>
       </c>
       <c r="U2" t="n">
         <v>0.0</v>
@@ -1914,13 +1926,13 @@
         <v>0.0</v>
       </c>
       <c r="W2" t="n">
-        <v>1480.0</v>
+        <v>0.0</v>
       </c>
       <c r="X2" t="n">
-        <v>185.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y2" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="Z2"/>
       <c r="AA2"/>
@@ -1928,35 +1940,35 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>253</v>
       </c>
       <c r="C3" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G3" t="s">
-        <v>167</v>
+        <v>254</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J3" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="K3" t="s">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="L3" t="n">
         <v>0.0</v>
@@ -1968,25 +1980,25 @@
       <c r="Q3"/>
       <c r="R3"/>
       <c r="S3" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="T3" t="s">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="U3" t="n">
-        <v>1528.0</v>
+        <v>1544.0</v>
       </c>
       <c r="V3" t="n">
-        <v>191.0</v>
+        <v>193.0</v>
       </c>
       <c r="W3" t="n">
-        <v>1528.0</v>
+        <v>1544.0</v>
       </c>
       <c r="X3" t="n">
-        <v>191.0</v>
+        <v>193.0</v>
       </c>
       <c r="Y3" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="Z3"/>
       <c r="AA3"/>
@@ -1994,35 +2006,35 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>257</v>
       </c>
       <c r="C4" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G4" t="s">
-        <v>162</v>
+        <v>249</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J4" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="K4" t="s">
-        <v>171</v>
+        <v>258</v>
       </c>
       <c r="L4" t="n">
         <v>0.0</v>
@@ -2034,25 +2046,25 @@
       <c r="Q4"/>
       <c r="R4"/>
       <c r="S4" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="T4" t="s">
-        <v>171</v>
+        <v>258</v>
       </c>
       <c r="U4" t="n">
-        <v>1536.0</v>
+        <v>1552.0</v>
       </c>
       <c r="V4" t="n">
-        <v>192.0</v>
+        <v>194.0</v>
       </c>
       <c r="W4" t="n">
-        <v>1536.0</v>
+        <v>1552.0</v>
       </c>
       <c r="X4" t="n">
-        <v>192.0</v>
+        <v>194.0</v>
       </c>
       <c r="Y4" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="Z4"/>
       <c r="AA4"/>
@@ -2060,35 +2072,35 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>259</v>
       </c>
       <c r="C5" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G5" t="s">
-        <v>167</v>
+        <v>254</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J5" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="K5" t="s">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="L5" t="n">
         <v>0.0</v>
@@ -2100,25 +2112,25 @@
       <c r="Q5"/>
       <c r="R5"/>
       <c r="S5" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="T5" t="s">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="U5" t="n">
-        <v>1528.0</v>
+        <v>1544.0</v>
       </c>
       <c r="V5" t="n">
-        <v>191.0</v>
+        <v>193.0</v>
       </c>
       <c r="W5" t="n">
-        <v>1528.0</v>
+        <v>1544.0</v>
       </c>
       <c r="X5" t="n">
-        <v>191.0</v>
+        <v>193.0</v>
       </c>
       <c r="Y5" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="Z5"/>
       <c r="AA5"/>
@@ -2126,35 +2138,35 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B6" t="s">
-        <v>173</v>
+        <v>260</v>
       </c>
       <c r="C6" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D6" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G6" t="s">
-        <v>174</v>
+        <v>261</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J6" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="K6" t="s">
-        <v>175</v>
+        <v>262</v>
       </c>
       <c r="L6" t="n">
         <v>0.0</v>
@@ -2166,10 +2178,10 @@
       <c r="Q6"/>
       <c r="R6"/>
       <c r="S6" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="T6" t="s">
-        <v>175</v>
+        <v>262</v>
       </c>
       <c r="U6" t="n">
         <v>0.0</v>
@@ -2178,13 +2190,13 @@
         <v>0.0</v>
       </c>
       <c r="W6" t="n">
-        <v>1480.0</v>
+        <v>0.0</v>
       </c>
       <c r="X6" t="n">
-        <v>185.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y6" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="Z6"/>
       <c r="AA6"/>
@@ -2192,35 +2204,35 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>263</v>
       </c>
       <c r="C7" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G7" t="s">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J7" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="K7" t="s">
-        <v>178</v>
+        <v>265</v>
       </c>
       <c r="L7" t="n">
         <v>0.0</v>
@@ -2232,25 +2244,25 @@
       <c r="Q7"/>
       <c r="R7"/>
       <c r="S7" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="T7" t="s">
-        <v>178</v>
+        <v>265</v>
       </c>
       <c r="U7" t="n">
-        <v>1504.0</v>
+        <v>1520.0</v>
       </c>
       <c r="V7" t="n">
-        <v>188.0</v>
+        <v>190.0</v>
       </c>
       <c r="W7" t="n">
-        <v>1504.0</v>
+        <v>1520.0</v>
       </c>
       <c r="X7" t="n">
-        <v>188.0</v>
+        <v>190.0</v>
       </c>
       <c r="Y7" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="Z7"/>
       <c r="AA7"/>
@@ -2258,35 +2270,35 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>266</v>
       </c>
       <c r="C8" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G8" t="s">
-        <v>174</v>
+        <v>261</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J8" t="s">
-        <v>180</v>
+        <v>267</v>
       </c>
       <c r="K8" t="s">
-        <v>181</v>
+        <v>268</v>
       </c>
       <c r="L8" t="n">
         <v>0.0</v>
@@ -2298,25 +2310,25 @@
       <c r="Q8"/>
       <c r="R8"/>
       <c r="S8" t="s">
-        <v>180</v>
+        <v>267</v>
       </c>
       <c r="T8" t="s">
-        <v>181</v>
+        <v>268</v>
       </c>
       <c r="U8" t="n">
-        <v>1480.0</v>
+        <v>0.0</v>
       </c>
       <c r="V8" t="n">
-        <v>185.0</v>
+        <v>0.0</v>
       </c>
       <c r="W8" t="n">
-        <v>1480.0</v>
+        <v>0.0</v>
       </c>
       <c r="X8" t="n">
-        <v>185.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y8" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="Z8"/>
       <c r="AA8"/>
@@ -2324,35 +2336,35 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>269</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G9" t="s">
-        <v>183</v>
+        <v>270</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J9" t="s">
-        <v>180</v>
+        <v>267</v>
       </c>
       <c r="K9" t="s">
-        <v>180</v>
+        <v>271</v>
       </c>
       <c r="L9" t="n">
         <v>0.0</v>
@@ -2364,25 +2376,25 @@
       <c r="Q9"/>
       <c r="R9"/>
       <c r="S9" t="s">
-        <v>180</v>
+        <v>267</v>
       </c>
       <c r="T9" t="s">
-        <v>180</v>
+        <v>271</v>
       </c>
       <c r="U9" t="n">
-        <v>1520.0</v>
+        <v>1528.0</v>
       </c>
       <c r="V9" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
       <c r="W9" t="n">
-        <v>1519.0</v>
+        <v>1528.0</v>
       </c>
       <c r="X9" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
       <c r="Y9" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="Z9"/>
       <c r="AA9"/>
@@ -2390,35 +2402,35 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s">
-        <v>184</v>
+        <v>272</v>
       </c>
       <c r="C10" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G10" t="s">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J10" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="K10" t="s">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="L10" t="n">
         <v>0.0</v>
@@ -2430,10 +2442,10 @@
       <c r="Q10"/>
       <c r="R10"/>
       <c r="S10" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="T10" t="s">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="U10" t="n">
         <v>0.0</v>
@@ -2442,13 +2454,13 @@
         <v>0.0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0</v>
+        <v>1504.0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0</v>
+        <v>188.0</v>
       </c>
       <c r="Y10" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="Z10"/>
       <c r="AA10"/>
@@ -2456,35 +2468,35 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
-        <v>185</v>
+        <v>273</v>
       </c>
       <c r="C11" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>261</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J11" t="s">
-        <v>186</v>
+        <v>274</v>
       </c>
       <c r="K11" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="L11" t="n">
         <v>0.0</v>
@@ -2496,25 +2508,25 @@
       <c r="Q11"/>
       <c r="R11"/>
       <c r="S11" t="s">
-        <v>186</v>
+        <v>274</v>
       </c>
       <c r="T11" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>1488.0</v>
+        <v>1504.0</v>
       </c>
       <c r="V11" t="n">
-        <v>186.0</v>
+        <v>188.0</v>
       </c>
       <c r="W11" t="n">
-        <v>1488.0</v>
+        <v>1504.0</v>
       </c>
       <c r="X11" t="n">
-        <v>186.0</v>
+        <v>188.0</v>
       </c>
       <c r="Y11" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="Z11"/>
       <c r="AA11"/>
@@ -2522,35 +2534,35 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>276</v>
       </c>
       <c r="C12" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G12" t="s">
-        <v>167</v>
+        <v>254</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J12" t="s">
-        <v>186</v>
+        <v>274</v>
       </c>
       <c r="K12" t="s">
-        <v>189</v>
+        <v>277</v>
       </c>
       <c r="L12" t="n">
         <v>0.0</v>
@@ -2562,25 +2574,25 @@
       <c r="Q12"/>
       <c r="R12"/>
       <c r="S12" t="s">
-        <v>186</v>
+        <v>274</v>
       </c>
       <c r="T12" t="s">
-        <v>189</v>
+        <v>277</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0</v>
+        <v>1512.0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0</v>
+        <v>189.0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0</v>
+        <v>1512.0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0</v>
+        <v>189.0</v>
       </c>
       <c r="Y12" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="Z12"/>
       <c r="AA12"/>
@@ -2588,35 +2600,35 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>190</v>
+        <v>278</v>
       </c>
       <c r="C13" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E13"/>
       <c r="F13" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G13" t="s">
-        <v>191</v>
+        <v>279</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J13" t="s">
-        <v>192</v>
+        <v>280</v>
       </c>
       <c r="K13" t="s">
-        <v>193</v>
+        <v>281</v>
       </c>
       <c r="L13" t="n">
         <v>0.0</v>
@@ -2628,10 +2640,10 @@
       <c r="Q13"/>
       <c r="R13"/>
       <c r="S13" t="s">
-        <v>192</v>
+        <v>280</v>
       </c>
       <c r="T13" t="s">
-        <v>193</v>
+        <v>281</v>
       </c>
       <c r="U13" t="n">
         <v>0.0</v>
@@ -2646,7 +2658,7 @@
         <v>0.0</v>
       </c>
       <c r="Y13" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="Z13"/>
       <c r="AA13"/>
@@ -2654,35 +2666,35 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B14" t="s">
-        <v>194</v>
+        <v>282</v>
       </c>
       <c r="C14" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E14"/>
       <c r="F14" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G14" t="s">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J14" t="s">
-        <v>195</v>
+        <v>283</v>
       </c>
       <c r="K14" t="s">
-        <v>196</v>
+        <v>284</v>
       </c>
       <c r="L14" t="n">
         <v>0.0</v>
@@ -2694,10 +2706,10 @@
       <c r="Q14"/>
       <c r="R14"/>
       <c r="S14" t="s">
-        <v>195</v>
+        <v>283</v>
       </c>
       <c r="T14" t="s">
-        <v>196</v>
+        <v>284</v>
       </c>
       <c r="U14" t="n">
         <v>0.0</v>
@@ -2712,7 +2724,7 @@
         <v>0.0</v>
       </c>
       <c r="Y14" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="Z14"/>
       <c r="AA14"/>
@@ -2720,35 +2732,35 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>285</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D15" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G15" t="s">
-        <v>162</v>
+        <v>249</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J15" t="s">
-        <v>198</v>
+        <v>286</v>
       </c>
       <c r="K15" t="s">
-        <v>199</v>
+        <v>287</v>
       </c>
       <c r="L15" t="n">
         <v>0.0</v>
@@ -2760,10 +2772,10 @@
       <c r="Q15"/>
       <c r="R15"/>
       <c r="S15" t="s">
-        <v>198</v>
+        <v>286</v>
       </c>
       <c r="T15" t="s">
-        <v>199</v>
+        <v>287</v>
       </c>
       <c r="U15" t="n">
         <v>0.0</v>
@@ -2778,7 +2790,7 @@
         <v>0.0</v>
       </c>
       <c r="Y15" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="Z15"/>
       <c r="AA15"/>
@@ -2786,35 +2798,35 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="C16" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D16" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>261</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J16" t="s">
-        <v>201</v>
+        <v>289</v>
       </c>
       <c r="K16" t="s">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="L16" t="n">
         <v>0.0</v>
@@ -2826,10 +2838,10 @@
       <c r="Q16"/>
       <c r="R16"/>
       <c r="S16" t="s">
-        <v>201</v>
+        <v>289</v>
       </c>
       <c r="T16" t="s">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="U16" t="n">
         <v>0.0</v>
@@ -2844,7 +2856,7 @@
         <v>0.0</v>
       </c>
       <c r="Y16" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="Z16"/>
       <c r="AA16"/>
@@ -2852,35 +2864,35 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>203</v>
+        <v>291</v>
       </c>
       <c r="C17" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D17" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G17" t="s">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J17" t="s">
-        <v>204</v>
+        <v>292</v>
       </c>
       <c r="K17" t="s">
-        <v>205</v>
+        <v>293</v>
       </c>
       <c r="L17" t="n">
         <v>0.0</v>
@@ -2892,10 +2904,10 @@
       <c r="Q17"/>
       <c r="R17"/>
       <c r="S17" t="s">
-        <v>204</v>
+        <v>292</v>
       </c>
       <c r="T17" t="s">
-        <v>205</v>
+        <v>293</v>
       </c>
       <c r="U17" t="n">
         <v>0.0</v>
@@ -2910,7 +2922,7 @@
         <v>0.0</v>
       </c>
       <c r="Y17" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="Z17"/>
       <c r="AA17"/>
@@ -2918,35 +2930,35 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>206</v>
+        <v>294</v>
       </c>
       <c r="C18" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D18" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G18" t="s">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J18" t="s">
-        <v>207</v>
+        <v>295</v>
       </c>
       <c r="K18" t="s">
-        <v>208</v>
+        <v>296</v>
       </c>
       <c r="L18" t="n">
         <v>0.0</v>
@@ -2958,10 +2970,10 @@
       <c r="Q18"/>
       <c r="R18"/>
       <c r="S18" t="s">
-        <v>207</v>
+        <v>295</v>
       </c>
       <c r="T18" t="s">
-        <v>208</v>
+        <v>296</v>
       </c>
       <c r="U18" t="n">
         <v>0.0</v>
@@ -2976,7 +2988,7 @@
         <v>0.0</v>
       </c>
       <c r="Y18" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="Z18"/>
       <c r="AA18"/>
@@ -2984,35 +2996,35 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B19" t="s">
-        <v>209</v>
+        <v>297</v>
       </c>
       <c r="C19" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E19"/>
       <c r="F19" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>261</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J19" t="s">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="K19" t="s">
-        <v>211</v>
+        <v>298</v>
       </c>
       <c r="L19" t="n">
         <v>0.0</v>
@@ -3024,25 +3036,25 @@
       <c r="Q19"/>
       <c r="R19"/>
       <c r="S19" t="s">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="T19" t="s">
-        <v>211</v>
+        <v>298</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0</v>
+        <v>1336.0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0</v>
+        <v>167.0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.0</v>
+        <v>1336.0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0</v>
+        <v>167.0</v>
       </c>
       <c r="Y19" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="Z19"/>
       <c r="AA19"/>
@@ -3050,35 +3062,35 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>212</v>
+        <v>299</v>
       </c>
       <c r="C20" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D20" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E20"/>
       <c r="F20" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G20" t="s">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J20" t="s">
-        <v>213</v>
+        <v>300</v>
       </c>
       <c r="K20" t="s">
-        <v>214</v>
+        <v>301</v>
       </c>
       <c r="L20" t="n">
         <v>0.0</v>
@@ -3090,10 +3102,10 @@
       <c r="Q20"/>
       <c r="R20"/>
       <c r="S20" t="s">
-        <v>213</v>
+        <v>300</v>
       </c>
       <c r="T20" t="s">
-        <v>214</v>
+        <v>301</v>
       </c>
       <c r="U20" t="n">
         <v>0.0</v>
@@ -3108,7 +3120,7 @@
         <v>0.0</v>
       </c>
       <c r="Y20" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="Z20"/>
       <c r="AA20"/>
@@ -3116,35 +3128,35 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>215</v>
+        <v>302</v>
       </c>
       <c r="C21" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E21"/>
       <c r="F21" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G21" t="s">
-        <v>216</v>
+        <v>261</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J21" t="s">
-        <v>217</v>
+        <v>303</v>
       </c>
       <c r="K21" t="s">
-        <v>218</v>
+        <v>304</v>
       </c>
       <c r="L21" t="n">
         <v>0.0</v>
@@ -3156,10 +3168,10 @@
       <c r="Q21"/>
       <c r="R21"/>
       <c r="S21" t="s">
-        <v>217</v>
+        <v>303</v>
       </c>
       <c r="T21" t="s">
-        <v>218</v>
+        <v>304</v>
       </c>
       <c r="U21" t="n">
         <v>0.0</v>
@@ -3174,7 +3186,7 @@
         <v>0.0</v>
       </c>
       <c r="Y21" t="s">
-        <v>143</v>
+        <v>74</v>
       </c>
       <c r="Z21"/>
       <c r="AA21"/>
@@ -3182,35 +3194,35 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B22" t="s">
-        <v>219</v>
+        <v>305</v>
       </c>
       <c r="C22" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E22"/>
       <c r="F22" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G22" t="s">
-        <v>162</v>
+        <v>306</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J22" t="s">
-        <v>220</v>
+        <v>307</v>
       </c>
       <c r="K22" t="s">
-        <v>221</v>
+        <v>308</v>
       </c>
       <c r="L22" t="n">
         <v>0.0</v>
@@ -3222,10 +3234,10 @@
       <c r="Q22"/>
       <c r="R22"/>
       <c r="S22" t="s">
-        <v>220</v>
+        <v>307</v>
       </c>
       <c r="T22" t="s">
-        <v>221</v>
+        <v>308</v>
       </c>
       <c r="U22" t="n">
         <v>0.0</v>
@@ -3240,7 +3252,7 @@
         <v>0.0</v>
       </c>
       <c r="Y22" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="Z22"/>
       <c r="AA22"/>
@@ -3248,35 +3260,35 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>222</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>223</v>
+        <v>309</v>
       </c>
       <c r="C23" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E23"/>
       <c r="F23" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G23" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J23" t="s">
-        <v>224</v>
+        <v>310</v>
       </c>
       <c r="K23" t="s">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="L23" t="n">
         <v>0.0</v>
@@ -3288,10 +3300,10 @@
       <c r="Q23"/>
       <c r="R23"/>
       <c r="S23" t="s">
-        <v>224</v>
+        <v>310</v>
       </c>
       <c r="T23" t="s">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="U23" t="n">
         <v>0.0</v>
@@ -3306,7 +3318,7 @@
         <v>0.0</v>
       </c>
       <c r="Y23" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="Z23"/>
       <c r="AA23"/>
@@ -3314,35 +3326,35 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>112</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s">
-        <v>226</v>
+        <v>312</v>
       </c>
       <c r="C24" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E24"/>
       <c r="F24" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G24" t="s">
-        <v>167</v>
+        <v>306</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J24" t="s">
-        <v>227</v>
+        <v>313</v>
       </c>
       <c r="K24" t="s">
-        <v>228</v>
+        <v>314</v>
       </c>
       <c r="L24" t="n">
         <v>0.0</v>
@@ -3354,10 +3366,10 @@
       <c r="Q24"/>
       <c r="R24"/>
       <c r="S24" t="s">
-        <v>227</v>
+        <v>313</v>
       </c>
       <c r="T24" t="s">
-        <v>228</v>
+        <v>314</v>
       </c>
       <c r="U24" t="n">
         <v>0.0</v>
@@ -3372,7 +3384,7 @@
         <v>0.0</v>
       </c>
       <c r="Y24" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="Z24"/>
       <c r="AA24"/>
@@ -3380,35 +3392,35 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>229</v>
+        <v>315</v>
       </c>
       <c r="C25" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D25" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E25"/>
       <c r="F25" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G25" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J25" t="s">
-        <v>231</v>
+        <v>316</v>
       </c>
       <c r="K25" t="s">
-        <v>232</v>
+        <v>317</v>
       </c>
       <c r="L25" t="n">
         <v>0.0</v>
@@ -3420,10 +3432,10 @@
       <c r="Q25"/>
       <c r="R25"/>
       <c r="S25" t="s">
-        <v>231</v>
+        <v>316</v>
       </c>
       <c r="T25" t="s">
-        <v>232</v>
+        <v>317</v>
       </c>
       <c r="U25" t="n">
         <v>0.0</v>
@@ -3438,7 +3450,7 @@
         <v>0.0</v>
       </c>
       <c r="Y25" t="s">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="Z25"/>
       <c r="AA25"/>
@@ -3446,35 +3458,35 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>233</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>234</v>
+        <v>318</v>
       </c>
       <c r="C26" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D26" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E26"/>
       <c r="F26" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G26" t="s">
-        <v>230</v>
+        <v>319</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J26" t="s">
-        <v>235</v>
+        <v>320</v>
       </c>
       <c r="K26" t="s">
-        <v>236</v>
+        <v>321</v>
       </c>
       <c r="L26" t="n">
         <v>0.0</v>
@@ -3486,10 +3498,10 @@
       <c r="Q26"/>
       <c r="R26"/>
       <c r="S26" t="s">
-        <v>235</v>
+        <v>320</v>
       </c>
       <c r="T26" t="s">
-        <v>236</v>
+        <v>321</v>
       </c>
       <c r="U26" t="n">
         <v>0.0</v>
@@ -3504,7 +3516,7 @@
         <v>0.0</v>
       </c>
       <c r="Y26" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="Z26"/>
       <c r="AA26"/>
@@ -3512,35 +3524,35 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s">
-        <v>237</v>
+        <v>322</v>
       </c>
       <c r="C27" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D27" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G27" t="s">
-        <v>230</v>
+        <v>319</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J27" t="s">
-        <v>238</v>
+        <v>323</v>
       </c>
       <c r="K27" t="s">
-        <v>239</v>
+        <v>324</v>
       </c>
       <c r="L27" t="n">
         <v>0.0</v>
@@ -3552,25 +3564,25 @@
       <c r="Q27"/>
       <c r="R27"/>
       <c r="S27" t="s">
-        <v>238</v>
+        <v>323</v>
       </c>
       <c r="T27" t="s">
-        <v>239</v>
+        <v>324</v>
       </c>
       <c r="U27" t="n">
-        <v>552.0</v>
+        <v>0.0</v>
       </c>
       <c r="V27" t="n">
-        <v>69.0</v>
+        <v>0.0</v>
       </c>
       <c r="W27" t="n">
-        <v>552.0</v>
+        <v>0.0</v>
       </c>
       <c r="X27" t="n">
-        <v>69.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y27" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="Z27"/>
       <c r="AA27"/>
@@ -3578,35 +3590,35 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>240</v>
+        <v>325</v>
       </c>
       <c r="C28" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D28" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E28"/>
       <c r="F28" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G28" t="s">
-        <v>241</v>
+        <v>319</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J28" t="s">
-        <v>238</v>
+        <v>326</v>
       </c>
       <c r="K28" t="s">
-        <v>242</v>
+        <v>327</v>
       </c>
       <c r="L28" t="n">
         <v>0.0</v>
@@ -3618,25 +3630,25 @@
       <c r="Q28"/>
       <c r="R28"/>
       <c r="S28" t="s">
-        <v>238</v>
+        <v>326</v>
       </c>
       <c r="T28" t="s">
-        <v>242</v>
+        <v>327</v>
       </c>
       <c r="U28" t="n">
-        <v>568.0</v>
+        <v>552.0</v>
       </c>
       <c r="V28" t="n">
-        <v>71.0</v>
+        <v>69.0</v>
       </c>
       <c r="W28" t="n">
-        <v>568.0</v>
+        <v>552.0</v>
       </c>
       <c r="X28" t="n">
-        <v>71.0</v>
+        <v>69.0</v>
       </c>
       <c r="Y28" t="s">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="Z28"/>
       <c r="AA28"/>
@@ -3644,35 +3656,35 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>243</v>
+        <v>328</v>
       </c>
       <c r="C29" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D29" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E29"/>
       <c r="F29" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G29" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J29" t="s">
-        <v>238</v>
+        <v>326</v>
       </c>
       <c r="K29" t="s">
-        <v>242</v>
+        <v>330</v>
       </c>
       <c r="L29" t="n">
         <v>0.0</v>
@@ -3684,25 +3696,25 @@
       <c r="Q29"/>
       <c r="R29"/>
       <c r="S29" t="s">
-        <v>238</v>
+        <v>326</v>
       </c>
       <c r="T29" t="s">
-        <v>242</v>
+        <v>330</v>
       </c>
       <c r="U29" t="n">
-        <v>0.0</v>
+        <v>568.0</v>
       </c>
       <c r="V29" t="n">
-        <v>0.0</v>
+        <v>71.0</v>
       </c>
       <c r="W29" t="n">
-        <v>184.0</v>
+        <v>568.0</v>
       </c>
       <c r="X29" t="n">
-        <v>23.0</v>
+        <v>71.0</v>
       </c>
       <c r="Y29" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="Z29"/>
       <c r="AA29"/>
@@ -3710,35 +3722,35 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B30" t="s">
-        <v>244</v>
+        <v>331</v>
       </c>
       <c r="C30" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D30" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E30"/>
       <c r="F30" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G30" t="s">
-        <v>245</v>
+        <v>329</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J30" t="s">
-        <v>246</v>
+        <v>326</v>
       </c>
       <c r="K30" t="s">
-        <v>247</v>
+        <v>330</v>
       </c>
       <c r="L30" t="n">
         <v>0.0</v>
@@ -3750,16 +3762,16 @@
       <c r="Q30"/>
       <c r="R30"/>
       <c r="S30" t="s">
-        <v>246</v>
+        <v>326</v>
       </c>
       <c r="T30" t="s">
-        <v>247</v>
+        <v>330</v>
       </c>
       <c r="U30" t="n">
-        <v>184.0</v>
+        <v>0.0</v>
       </c>
       <c r="V30" t="n">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
       <c r="W30" t="n">
         <v>184.0</v>
@@ -3768,7 +3780,7 @@
         <v>23.0</v>
       </c>
       <c r="Y30" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="Z30"/>
       <c r="AA30"/>
@@ -3776,35 +3788,35 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B31" t="s">
+        <v>332</v>
+      </c>
+      <c r="C31" t="s">
+        <v>247</v>
+      </c>
+      <c r="D31" t="s">
         <v>248</v>
-      </c>
-      <c r="C31" t="s">
-        <v>159</v>
-      </c>
-      <c r="D31" t="s">
-        <v>160</v>
       </c>
       <c r="E31"/>
       <c r="F31" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G31" t="s">
-        <v>249</v>
+        <v>333</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J31" t="s">
-        <v>238</v>
+        <v>334</v>
       </c>
       <c r="K31" t="s">
-        <v>250</v>
+        <v>335</v>
       </c>
       <c r="L31" t="n">
         <v>0.0</v>
@@ -3816,25 +3828,25 @@
       <c r="Q31"/>
       <c r="R31"/>
       <c r="S31" t="s">
-        <v>238</v>
+        <v>334</v>
       </c>
       <c r="T31" t="s">
-        <v>250</v>
+        <v>335</v>
       </c>
       <c r="U31" t="n">
-        <v>0.0</v>
+        <v>184.0</v>
       </c>
       <c r="V31" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
       <c r="W31" t="n">
-        <v>0.0</v>
+        <v>184.0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
       <c r="Y31" t="s">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="Z31"/>
       <c r="AA31"/>
@@ -3842,35 +3854,35 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B32" t="s">
-        <v>251</v>
+        <v>336</v>
       </c>
       <c r="C32" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D32" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E32"/>
       <c r="F32" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G32" t="s">
-        <v>230</v>
+        <v>337</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J32" t="s">
-        <v>252</v>
+        <v>326</v>
       </c>
       <c r="K32" t="s">
-        <v>253</v>
+        <v>338</v>
       </c>
       <c r="L32" t="n">
         <v>0.0</v>
@@ -3882,10 +3894,10 @@
       <c r="Q32"/>
       <c r="R32"/>
       <c r="S32" t="s">
-        <v>252</v>
+        <v>326</v>
       </c>
       <c r="T32" t="s">
-        <v>253</v>
+        <v>338</v>
       </c>
       <c r="U32" t="n">
         <v>0.0</v>
@@ -3900,7 +3912,7 @@
         <v>0.0</v>
       </c>
       <c r="Y32" t="s">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="Z32"/>
       <c r="AA32"/>
@@ -3908,35 +3920,35 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B33" t="s">
-        <v>254</v>
+        <v>339</v>
       </c>
       <c r="C33" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D33" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E33"/>
       <c r="F33" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G33" t="s">
-        <v>177</v>
+        <v>319</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J33" t="s">
-        <v>255</v>
+        <v>340</v>
       </c>
       <c r="K33" t="s">
-        <v>256</v>
+        <v>341</v>
       </c>
       <c r="L33" t="n">
         <v>0.0</v>
@@ -3948,10 +3960,10 @@
       <c r="Q33"/>
       <c r="R33"/>
       <c r="S33" t="s">
-        <v>255</v>
+        <v>340</v>
       </c>
       <c r="T33" t="s">
-        <v>256</v>
+        <v>341</v>
       </c>
       <c r="U33" t="n">
         <v>0.0</v>
@@ -3966,7 +3978,7 @@
         <v>0.0</v>
       </c>
       <c r="Y33" t="s">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="Z33"/>
       <c r="AA33"/>
@@ -3974,35 +3986,35 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B34" t="s">
-        <v>257</v>
+        <v>342</v>
       </c>
       <c r="C34" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D34" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E34"/>
       <c r="F34" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G34" t="s">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J34" t="s">
-        <v>258</v>
+        <v>343</v>
       </c>
       <c r="K34" t="s">
-        <v>259</v>
+        <v>344</v>
       </c>
       <c r="L34" t="n">
         <v>0.0</v>
@@ -4014,10 +4026,10 @@
       <c r="Q34"/>
       <c r="R34"/>
       <c r="S34" t="s">
-        <v>258</v>
+        <v>343</v>
       </c>
       <c r="T34" t="s">
-        <v>259</v>
+        <v>344</v>
       </c>
       <c r="U34" t="n">
         <v>0.0</v>
@@ -4032,7 +4044,7 @@
         <v>0.0</v>
       </c>
       <c r="Y34" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="Z34"/>
       <c r="AA34"/>
@@ -4040,35 +4052,35 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B35" t="s">
-        <v>260</v>
+        <v>345</v>
       </c>
       <c r="C35" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E35"/>
       <c r="F35" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G35" t="s">
-        <v>174</v>
+        <v>264</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J35" t="s">
-        <v>261</v>
+        <v>346</v>
       </c>
       <c r="K35" t="s">
-        <v>262</v>
+        <v>347</v>
       </c>
       <c r="L35" t="n">
         <v>0.0</v>
@@ -4080,10 +4092,10 @@
       <c r="Q35"/>
       <c r="R35"/>
       <c r="S35" t="s">
-        <v>261</v>
+        <v>346</v>
       </c>
       <c r="T35" t="s">
-        <v>262</v>
+        <v>347</v>
       </c>
       <c r="U35" t="n">
         <v>0.0</v>
@@ -4098,7 +4110,7 @@
         <v>0.0</v>
       </c>
       <c r="Y35" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="Z35"/>
       <c r="AA35"/>
@@ -4106,35 +4118,35 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B36" t="s">
-        <v>263</v>
+        <v>348</v>
       </c>
       <c r="C36" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D36" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E36"/>
       <c r="F36" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G36" t="s">
-        <v>174</v>
+        <v>261</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J36" t="s">
-        <v>255</v>
+        <v>349</v>
       </c>
       <c r="K36" t="s">
-        <v>264</v>
+        <v>350</v>
       </c>
       <c r="L36" t="n">
         <v>0.0</v>
@@ -4146,25 +4158,25 @@
       <c r="Q36"/>
       <c r="R36"/>
       <c r="S36" t="s">
-        <v>255</v>
+        <v>349</v>
       </c>
       <c r="T36" t="s">
-        <v>264</v>
+        <v>350</v>
       </c>
       <c r="U36" t="n">
-        <v>224.0</v>
+        <v>0.0</v>
       </c>
       <c r="V36" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="W36" t="n">
-        <v>224.0</v>
+        <v>0.0</v>
       </c>
       <c r="X36" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y36" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="Z36"/>
       <c r="AA36"/>
@@ -4172,35 +4184,35 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>265</v>
+        <v>141</v>
       </c>
       <c r="B37" t="s">
-        <v>266</v>
+        <v>351</v>
       </c>
       <c r="C37" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E37"/>
       <c r="F37" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G37" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="J37" t="s">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="K37" t="s">
-        <v>268</v>
+        <v>352</v>
       </c>
       <c r="L37" t="n">
         <v>0.0</v>
@@ -4212,29 +4224,95 @@
       <c r="Q37"/>
       <c r="R37"/>
       <c r="S37" t="s">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="T37" t="s">
-        <v>268</v>
+        <v>352</v>
       </c>
       <c r="U37" t="n">
-        <v>0.0</v>
+        <v>224.0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.0</v>
+        <v>28.0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.0</v>
+        <v>224.0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0</v>
+        <v>28.0</v>
       </c>
       <c r="Y37" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="Z37"/>
       <c r="AA37"/>
       <c r="AB37"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>245</v>
+      </c>
+      <c r="B38" t="s">
+        <v>353</v>
+      </c>
+      <c r="C38" t="s">
+        <v>247</v>
+      </c>
+      <c r="D38" t="s">
+        <v>248</v>
+      </c>
+      <c r="E38"/>
+      <c r="F38" t="s">
+        <v>143</v>
+      </c>
+      <c r="G38" t="s">
+        <v>329</v>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="s">
+        <v>250</v>
+      </c>
+      <c r="J38" t="s">
+        <v>354</v>
+      </c>
+      <c r="K38" t="s">
+        <v>355</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+      <c r="P38"/>
+      <c r="Q38"/>
+      <c r="R38"/>
+      <c r="S38" t="s">
+        <v>354</v>
+      </c>
+      <c r="T38" t="s">
+        <v>355</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z38"/>
+      <c r="AA38"/>
+      <c r="AB38"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4277,13 +4355,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D2" t="n">
         <v>0.0</v>
@@ -4291,13 +4369,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D3" t="n">
         <v>0.0</v>
@@ -4305,13 +4383,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D4" t="n">
         <v>0.0</v>
@@ -4319,13 +4397,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D5" t="n">
         <v>0.0</v>
@@ -4333,13 +4411,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D6" t="n">
         <v>0.0</v>
@@ -4347,13 +4425,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D7" t="n">
         <v>0.0</v>
@@ -4361,13 +4439,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D8" t="n">
         <v>0.0</v>
@@ -4375,13 +4453,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C9" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D9" t="n">
         <v>0.0</v>
@@ -4389,13 +4467,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
         <v>0.0</v>
@@ -4403,13 +4481,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C11" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D11" t="n">
         <v>0.0</v>
@@ -4417,13 +4495,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C12" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D12" t="n">
         <v>0.0</v>
@@ -4431,13 +4509,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D13" t="n">
         <v>0.0</v>
@@ -4445,13 +4523,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D14" t="n">
         <v>0.0</v>
@@ -4459,13 +4537,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C15" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D15" t="n">
         <v>0.0</v>
@@ -4473,13 +4551,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s">
-        <v>222</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D16" t="n">
         <v>0.0</v>
@@ -4487,13 +4565,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D17" t="n">
         <v>0.0</v>
@@ -4501,13 +4579,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C18" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D18" t="n">
         <v>0.0</v>
@@ -4515,13 +4593,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D19" t="n">
         <v>0.0</v>
@@ -4529,13 +4607,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D20" t="n">
         <v>0.0</v>
@@ -4543,13 +4621,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>243</v>
       </c>
       <c r="C21" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D21" t="n">
         <v>0.0</v>
@@ -4557,13 +4635,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C22" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D22" t="n">
         <v>0.0</v>
@@ -4571,13 +4649,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D23" t="n">
         <v>0.0</v>
@@ -4585,13 +4663,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B24" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C24" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D24" t="n">
         <v>0.0</v>
@@ -4599,13 +4677,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C25" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D25" t="n">
         <v>0.0</v>
@@ -4613,13 +4691,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="C26" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D26" t="n">
         <v>0.0</v>
@@ -4627,13 +4705,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C27" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D27" t="n">
         <v>0.0</v>
@@ -4641,13 +4719,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D28" t="n">
         <v>0.0</v>
@@ -4655,13 +4733,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B29" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="C29" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D29" t="n">
         <v>0.0</v>
@@ -4669,13 +4747,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D30" t="n">
         <v>0.0</v>
@@ -4683,13 +4761,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D31" t="n">
         <v>0.0</v>
@@ -4697,13 +4775,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D32" t="n">
         <v>0.0</v>
@@ -4711,13 +4789,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="C33" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D33" t="n">
         <v>0.0</v>
@@ -4725,13 +4803,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="C34" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D34" t="n">
         <v>0.0</v>
@@ -4739,13 +4817,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D35" t="n">
         <v>0.0</v>
@@ -4753,13 +4831,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C36" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D36" t="n">
         <v>0.0</v>
@@ -4767,13 +4845,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B37" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="C37" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D37" t="n">
         <v>0.0</v>
@@ -4856,10 +4934,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>289</v>
+        <v>142</v>
       </c>
       <c r="C2" t="n">
         <v>1.0</v>
@@ -4877,7 +4955,7 @@
         <v>300.0</v>
       </c>
       <c r="H2" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -4888,15 +4966,15 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>291</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s">
-        <v>292</v>
+        <v>146</v>
       </c>
       <c r="C3" t="n">
         <v>1.0</v>
@@ -4914,7 +4992,7 @@
         <v>240.0</v>
       </c>
       <c r="H3" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -4928,10 +5006,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>293</v>
+        <v>147</v>
       </c>
       <c r="C4" t="n">
         <v>1.0</v>
@@ -4949,7 +5027,7 @@
         <v>520.0</v>
       </c>
       <c r="H4" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -4960,15 +5038,15 @@
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>294</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>295</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>296</v>
+        <v>150</v>
       </c>
       <c r="C5" t="n">
         <v>1.0</v>
@@ -4986,7 +5064,7 @@
         <v>490.0</v>
       </c>
       <c r="H5" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -4997,15 +5075,15 @@
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>297</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>298</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
-        <v>299</v>
+        <v>153</v>
       </c>
       <c r="C6" t="n">
         <v>1.0</v>
@@ -5023,7 +5101,7 @@
         <v>560.0</v>
       </c>
       <c r="H6" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -5034,15 +5112,15 @@
         <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>300</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>301</v>
+        <v>155</v>
       </c>
       <c r="B7" t="s">
-        <v>302</v>
+        <v>156</v>
       </c>
       <c r="C7" t="n">
         <v>1.0</v>
@@ -5060,7 +5138,7 @@
         <v>350.0</v>
       </c>
       <c r="H7" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -5071,15 +5149,15 @@
         <v>0</v>
       </c>
       <c r="M7" t="s">
-        <v>303</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
-        <v>304</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
         <v>1.0</v>
@@ -5097,7 +5175,7 @@
         <v>320.0</v>
       </c>
       <c r="H8" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -5108,15 +5186,15 @@
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>305</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>306</v>
+        <v>160</v>
       </c>
       <c r="B9" t="s">
-        <v>307</v>
+        <v>161</v>
       </c>
       <c r="C9" t="n">
         <v>2.0</v>
@@ -5134,7 +5212,7 @@
         <v>0.0</v>
       </c>
       <c r="H9" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -5145,15 +5223,15 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>308</v>
+        <v>162</v>
       </c>
       <c r="B10" t="s">
-        <v>309</v>
+        <v>163</v>
       </c>
       <c r="C10" t="n">
         <v>2.0</v>
@@ -5171,7 +5249,7 @@
         <v>0.0</v>
       </c>
       <c r="H10" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -5182,15 +5260,15 @@
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>310</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B11" t="s">
-        <v>311</v>
+        <v>166</v>
       </c>
       <c r="C11" t="n">
         <v>1.0</v>
@@ -5208,7 +5286,7 @@
         <v>360.0</v>
       </c>
       <c r="H11" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -5219,15 +5297,15 @@
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>312</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B12" t="s">
-        <v>313</v>
+        <v>168</v>
       </c>
       <c r="C12" t="n">
         <v>1.0</v>
@@ -5245,7 +5323,7 @@
         <v>480.0</v>
       </c>
       <c r="H12" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -5256,15 +5334,15 @@
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s">
-        <v>314</v>
+        <v>169</v>
       </c>
       <c r="C13" t="n">
         <v>1.0</v>
@@ -5282,7 +5360,7 @@
         <v>300.0</v>
       </c>
       <c r="H13" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -5293,15 +5371,15 @@
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>286</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B14" t="s">
-        <v>315</v>
+        <v>171</v>
       </c>
       <c r="C14" t="n">
         <v>1.0</v>
@@ -5319,7 +5397,7 @@
         <v>450.0</v>
       </c>
       <c r="H14" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -5330,15 +5408,15 @@
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>316</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s">
-        <v>317</v>
+        <v>173</v>
       </c>
       <c r="C15" t="n">
         <v>1.0</v>
@@ -5356,7 +5434,7 @@
         <v>450.0</v>
       </c>
       <c r="H15" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -5367,15 +5445,15 @@
         <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>318</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s">
-        <v>319</v>
+        <v>175</v>
       </c>
       <c r="C16" t="n">
         <v>1.0</v>
@@ -5393,7 +5471,7 @@
         <v>450.0</v>
       </c>
       <c r="H16" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -5404,15 +5482,15 @@
         <v>0</v>
       </c>
       <c r="M16" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>320</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s">
-        <v>321</v>
+        <v>177</v>
       </c>
       <c r="C17" t="n">
         <v>1.0</v>
@@ -5430,7 +5508,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -5441,15 +5519,15 @@
         <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>322</v>
+        <v>178</v>
       </c>
       <c r="B18" t="s">
-        <v>323</v>
+        <v>179</v>
       </c>
       <c r="C18" t="n">
         <v>1.0</v>
@@ -5467,7 +5545,7 @@
         <v>330.0</v>
       </c>
       <c r="H18" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
@@ -5481,10 +5559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>324</v>
+        <v>180</v>
       </c>
       <c r="B19" t="s">
-        <v>325</v>
+        <v>181</v>
       </c>
       <c r="C19" t="n">
         <v>1.0</v>
@@ -5502,7 +5580,7 @@
         <v>260.0</v>
       </c>
       <c r="H19" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -5513,15 +5591,15 @@
         <v>0</v>
       </c>
       <c r="M19" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B20" t="s">
-        <v>326</v>
+        <v>182</v>
       </c>
       <c r="C20" t="n">
         <v>1.0</v>
@@ -5539,7 +5617,7 @@
         <v>450.0</v>
       </c>
       <c r="H20" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -5550,15 +5628,15 @@
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>327</v>
+        <v>183</v>
       </c>
       <c r="B21" t="s">
-        <v>328</v>
+        <v>184</v>
       </c>
       <c r="C21" t="n">
         <v>1.0</v>
@@ -5576,7 +5654,7 @@
         <v>360.0</v>
       </c>
       <c r="H21" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
@@ -5590,10 +5668,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>329</v>
+        <v>185</v>
       </c>
       <c r="B22" t="s">
-        <v>330</v>
+        <v>186</v>
       </c>
       <c r="C22" t="n">
         <v>2.0</v>
@@ -5611,7 +5689,7 @@
         <v>360.0</v>
       </c>
       <c r="H22" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -5622,15 +5700,15 @@
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B23" t="s">
-        <v>331</v>
+        <v>187</v>
       </c>
       <c r="C23" t="n">
         <v>1.0</v>
@@ -5648,7 +5726,7 @@
         <v>260.0</v>
       </c>
       <c r="H23" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -5659,15 +5737,15 @@
         <v>0</v>
       </c>
       <c r="M23" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>332</v>
+        <v>188</v>
       </c>
       <c r="B24" t="s">
-        <v>333</v>
+        <v>189</v>
       </c>
       <c r="C24" t="n">
         <v>1.0</v>
@@ -5685,7 +5763,7 @@
         <v>600.0</v>
       </c>
       <c r="H24" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -5699,10 +5777,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>273</v>
+        <v>190</v>
       </c>
       <c r="B25" t="s">
-        <v>285</v>
+        <v>191</v>
       </c>
       <c r="C25" t="n">
         <v>1.0</v>
@@ -5720,7 +5798,7 @@
         <v>250.0</v>
       </c>
       <c r="H25" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I25" t="b">
         <v>1</v>
@@ -5731,15 +5809,15 @@
         <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s">
-        <v>334</v>
+        <v>192</v>
       </c>
       <c r="C26" t="n">
         <v>1.0</v>
@@ -5757,7 +5835,7 @@
         <v>450.0</v>
       </c>
       <c r="H26" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -5768,15 +5846,15 @@
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>335</v>
+        <v>193</v>
       </c>
       <c r="B27" t="s">
-        <v>336</v>
+        <v>194</v>
       </c>
       <c r="C27" t="n">
         <v>1.0</v>
@@ -5794,7 +5872,7 @@
         <v>560.0</v>
       </c>
       <c r="H27" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -5805,15 +5883,15 @@
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>337</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>338</v>
+        <v>196</v>
       </c>
       <c r="B28" t="s">
-        <v>339</v>
+        <v>197</v>
       </c>
       <c r="C28"/>
       <c r="D28" t="n">
@@ -5829,7 +5907,7 @@
         <v>2.0</v>
       </c>
       <c r="H28" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="I28" t="b">
         <v>1</v>
@@ -5840,15 +5918,15 @@
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>340</v>
+        <v>198</v>
       </c>
       <c r="B29" t="s">
-        <v>341</v>
+        <v>199</v>
       </c>
       <c r="C29" t="n">
         <v>1.0</v>
@@ -5866,7 +5944,7 @@
         <v>390.0</v>
       </c>
       <c r="H29" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -5877,15 +5955,15 @@
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
-        <v>342</v>
+        <v>200</v>
       </c>
       <c r="C30" t="n">
         <v>1.0</v>
@@ -5903,7 +5981,7 @@
         <v>360.0</v>
       </c>
       <c r="H30" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -5914,15 +5992,15 @@
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>343</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B31" t="s">
-        <v>344</v>
+        <v>202</v>
       </c>
       <c r="C31" t="n">
         <v>1.0</v>
@@ -5940,7 +6018,7 @@
         <v>240.0</v>
       </c>
       <c r="H31" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -5951,15 +6029,15 @@
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>345</v>
+        <v>203</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>346</v>
+        <v>204</v>
       </c>
       <c r="B32" t="s">
-        <v>347</v>
+        <v>205</v>
       </c>
       <c r="C32" t="n">
         <v>1.0</v>
@@ -5977,7 +6055,7 @@
         <v>420.0</v>
       </c>
       <c r="H32" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -5991,10 +6069,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>348</v>
+        <v>206</v>
       </c>
       <c r="B33" t="s">
-        <v>349</v>
+        <v>207</v>
       </c>
       <c r="C33" t="n">
         <v>1.0</v>
@@ -6012,7 +6090,7 @@
         <v>420.0</v>
       </c>
       <c r="H33" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -6026,10 +6104,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B34" t="s">
-        <v>350</v>
+        <v>208</v>
       </c>
       <c r="C34" t="n">
         <v>1.0</v>
@@ -6047,7 +6125,7 @@
         <v>420.0</v>
       </c>
       <c r="H34" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -6058,15 +6136,15 @@
         <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>351</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B35" t="s">
-        <v>352</v>
+        <v>210</v>
       </c>
       <c r="C35" t="n">
         <v>1.0</v>
@@ -6084,7 +6162,7 @@
         <v>300.0</v>
       </c>
       <c r="H35" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -6095,15 +6173,15 @@
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>353</v>
+        <v>211</v>
       </c>
       <c r="B36" t="s">
-        <v>354</v>
+        <v>212</v>
       </c>
       <c r="C36" t="n">
         <v>1.0</v>
@@ -6121,7 +6199,7 @@
         <v>180.0</v>
       </c>
       <c r="H36" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -6132,15 +6210,15 @@
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>355</v>
+        <v>213</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>356</v>
+        <v>214</v>
       </c>
       <c r="B37" t="s">
-        <v>357</v>
+        <v>215</v>
       </c>
       <c r="C37" t="n">
         <v>1.0</v>
@@ -6158,7 +6236,7 @@
         <v>170.0</v>
       </c>
       <c r="H37" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I37" t="b">
         <v>1</v>
@@ -6169,15 +6247,15 @@
         <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B38" t="s">
-        <v>359</v>
+        <v>217</v>
       </c>
       <c r="C38" t="n">
         <v>1.0</v>
@@ -6195,7 +6273,7 @@
         <v>240.0</v>
       </c>
       <c r="H38" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
@@ -6206,15 +6284,15 @@
         <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>360</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B39" t="s">
-        <v>361</v>
+        <v>219</v>
       </c>
       <c r="C39" t="n">
         <v>1.0</v>
@@ -6232,7 +6310,7 @@
         <v>320.0</v>
       </c>
       <c r="H39" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -6243,15 +6321,15 @@
         <v>0</v>
       </c>
       <c r="M39" t="s">
-        <v>362</v>
+        <v>220</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>363</v>
+        <v>221</v>
       </c>
       <c r="B40" t="s">
-        <v>364</v>
+        <v>222</v>
       </c>
       <c r="C40" t="n">
         <v>1.0</v>
@@ -6269,7 +6347,7 @@
         <v>280.0</v>
       </c>
       <c r="H40" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -6280,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="s">
-        <v>365</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -6299,7 +6377,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:H43"/>
+  <dimension ref="A2:H44"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="8" max="8" customWidth="true" hidden="false" style="0" width="20.0" collapsed="false" outlineLevel="0"/>
@@ -6340,10 +6418,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
@@ -6356,10 +6434,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -6372,10 +6450,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C4" t="b">
         <v>0</v>
@@ -6388,10 +6466,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C5" t="b">
         <v>0</v>
@@ -6404,10 +6482,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -6420,10 +6498,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -6436,10 +6514,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
@@ -6452,10 +6530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -6468,10 +6546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -6484,10 +6562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>
@@ -6500,10 +6578,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C12" t="b">
         <v>1</v>
@@ -6516,10 +6594,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
@@ -6532,10 +6610,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C14" t="b">
         <v>1</v>
@@ -6548,10 +6626,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C15" t="b">
         <v>1</v>
@@ -6564,10 +6642,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C16" t="b">
         <v>0</v>
@@ -6580,10 +6658,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C17" t="b">
         <v>1</v>
@@ -6596,10 +6674,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C18" t="b">
         <v>1</v>
@@ -6612,10 +6690,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C19" t="b">
         <v>0</v>
@@ -6628,10 +6706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C20" t="b">
         <v>0</v>
@@ -6644,10 +6722,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C21" t="b">
         <v>0</v>
@@ -6660,10 +6738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C22" t="b">
         <v>0</v>
@@ -6676,10 +6754,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C23" t="b">
         <v>0</v>
@@ -6692,10 +6770,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C24" t="b">
         <v>0</v>
@@ -6708,10 +6786,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C25" t="b">
         <v>0</v>
@@ -6724,10 +6802,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C26" t="b">
         <v>0</v>
@@ -6740,13 +6818,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>1.0</v>
@@ -6756,10 +6834,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C28" t="b">
         <v>1</v>
@@ -6772,13 +6850,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="C29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>1.0</v>
@@ -6788,13 +6866,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="C30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>1.0</v>
@@ -6804,13 +6882,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>1.0</v>
@@ -6820,10 +6898,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B32" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
@@ -6836,13 +6914,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>1.0</v>
@@ -6852,10 +6930,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C34" t="b">
         <v>1</v>
@@ -6868,13 +6946,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="C35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
         <v>1.0</v>
@@ -6884,10 +6962,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="C36" t="b">
         <v>0</v>
@@ -6900,10 +6978,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C37" t="b">
         <v>0</v>
@@ -6916,13 +6994,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>1.0</v>
@@ -6932,10 +7010,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B39" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C39" t="b">
         <v>1</v>
@@ -6948,13 +7026,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B40" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="C40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
         <v>1.0</v>
@@ -6964,10 +7042,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="C41" t="b">
         <v>0</v>
@@ -6980,10 +7058,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B42" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C42" t="b">
         <v>0</v>
@@ -6996,19 +7074,35 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B43" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>1.0</v>
       </c>
       <c r="G43"/>
       <c r="H43"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>141</v>
+      </c>
+      <c r="B44" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" t="b">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G44"/>
+      <c r="H44"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7063,13 +7157,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>356</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>357</v>
       </c>
       <c r="C2" t="s">
-        <v>133</v>
+        <v>358</v>
       </c>
       <c r="D2" t="n">
         <v>999999.0</v>
@@ -7184,10 +7278,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>271</v>
+        <v>240</v>
       </c>
       <c r="B2" t="s">
-        <v>275</v>
+        <v>359</v>
       </c>
       <c r="C2" t="n">
         <v>1.0</v>
@@ -7201,7 +7295,7 @@
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -7210,10 +7304,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="B3" t="s">
-        <v>277</v>
+        <v>360</v>
       </c>
       <c r="C3" t="n">
         <v>1.0</v>
@@ -7227,7 +7321,7 @@
       <c r="F3"/>
       <c r="G3"/>
       <c r="H3" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -7236,10 +7330,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>278</v>
+        <v>361</v>
       </c>
       <c r="B4" t="s">
-        <v>279</v>
+        <v>362</v>
       </c>
       <c r="C4" t="n">
         <v>1.0</v>
@@ -7253,7 +7347,7 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -7262,10 +7356,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>280</v>
+        <v>363</v>
       </c>
       <c r="B5" t="s">
-        <v>281</v>
+        <v>364</v>
       </c>
       <c r="C5" t="n">
         <v>4.0</v>
@@ -7279,7 +7373,7 @@
       <c r="F5"/>
       <c r="G5"/>
       <c r="H5" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -7288,10 +7382,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>269</v>
+        <v>238</v>
       </c>
       <c r="B6" t="s">
-        <v>282</v>
+        <v>365</v>
       </c>
       <c r="C6" t="n">
         <v>2.0</v>
@@ -7305,7 +7399,7 @@
       <c r="F6"/>
       <c r="G6"/>
       <c r="H6" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -7314,10 +7408,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>283</v>
+        <v>366</v>
       </c>
       <c r="B7" t="s">
-        <v>284</v>
+        <v>367</v>
       </c>
       <c r="C7" t="n">
         <v>2.0</v>
@@ -7331,7 +7425,7 @@
       <c r="F7"/>
       <c r="G7"/>
       <c r="H7" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -7340,10 +7434,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>273</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
-        <v>285</v>
+        <v>191</v>
       </c>
       <c r="C8" t="n">
         <v>1.0</v>
@@ -7359,21 +7453,21 @@
         <v>0.0</v>
       </c>
       <c r="H8" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>286</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>287</v>
+        <v>368</v>
       </c>
       <c r="B9" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="C9" t="n">
         <v>4.0</v>
@@ -7387,7 +7481,7 @@
       <c r="F9"/>
       <c r="G9"/>
       <c r="H9" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -7431,101 +7525,101 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>269</v>
+        <v>238</v>
       </c>
       <c r="C2" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>240</v>
       </c>
       <c r="C3" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="C4" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="C5" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B6" t="s">
-        <v>271</v>
+        <v>240</v>
       </c>
       <c r="C6" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s">
-        <v>273</v>
+        <v>190</v>
       </c>
       <c r="C7" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s">
-        <v>273</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s">
-        <v>273</v>
+        <v>190</v>
       </c>
       <c r="C9" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s">
-        <v>273</v>
+        <v>190</v>
       </c>
       <c r="C10" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
